--- a/artfynd/A 31349-2026 artfynd.xlsx
+++ b/artfynd/A 31349-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724189</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135724197</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135724214</v>
       </c>
       <c r="B4" t="n">
-        <v>92434</v>
+        <v>92436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>135724184</v>
       </c>
       <c r="B5" t="n">
-        <v>91592</v>
+        <v>91594</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>135724190</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>135724198</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135724243</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>135724242</v>
       </c>
       <c r="B9" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>135724182</v>
       </c>
       <c r="B10" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135724183</v>
       </c>
       <c r="B11" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>135724188</v>
       </c>
       <c r="B12" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>135724192</v>
       </c>
       <c r="B13" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>135724194</v>
       </c>
       <c r="B14" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>135724211</v>
       </c>
       <c r="B15" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135724212</v>
       </c>
       <c r="B16" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135724220</v>
       </c>
       <c r="B17" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135724227</v>
       </c>
       <c r="B18" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135724230</v>
       </c>
       <c r="B19" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>135724234</v>
       </c>
       <c r="B20" t="n">
-        <v>89290</v>
+        <v>89292</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>135724206</v>
       </c>
       <c r="B21" t="n">
-        <v>91580</v>
+        <v>91582</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>135724215</v>
       </c>
       <c r="B38" t="n">
-        <v>99173</v>
+        <v>99175</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>135724196</v>
       </c>
       <c r="B39" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>135724202</v>
       </c>
       <c r="B40" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>135724203</v>
       </c>
       <c r="B41" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>135724204</v>
       </c>
       <c r="B42" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135724205</v>
       </c>
       <c r="B43" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>135724207</v>
       </c>
       <c r="B44" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>135724213</v>
       </c>
       <c r="B45" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>135724218</v>
       </c>
       <c r="B46" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>135724223</v>
       </c>
       <c r="B47" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135724236</v>
       </c>
       <c r="B48" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>135724237</v>
       </c>
       <c r="B49" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>135724238</v>
       </c>
       <c r="B50" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>135724241</v>
       </c>
       <c r="B51" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>135724187</v>
       </c>
       <c r="B52" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>135724191</v>
       </c>
       <c r="B53" t="n">
-        <v>99551</v>
+        <v>99553</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>135724199</v>
       </c>
       <c r="B54" t="n">
-        <v>99551</v>
+        <v>99553</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>135724186</v>
       </c>
       <c r="B55" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135724200</v>
       </c>
       <c r="B56" t="n">
-        <v>92440</v>
+        <v>92442</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135724195</v>
       </c>
       <c r="B57" t="n">
-        <v>93368</v>
+        <v>93370</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 31349-2026 artfynd.xlsx
+++ b/artfynd/A 31349-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724189</v>
       </c>
       <c r="B2" t="n">
-        <v>92000</v>
+        <v>92014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135724197</v>
       </c>
       <c r="B3" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135724214</v>
       </c>
       <c r="B4" t="n">
-        <v>92436</v>
+        <v>92450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>135724184</v>
       </c>
       <c r="B5" t="n">
-        <v>91594</v>
+        <v>91596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>135724190</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>135724198</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135724243</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>135724242</v>
       </c>
       <c r="B9" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>135724182</v>
       </c>
       <c r="B10" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135724183</v>
       </c>
       <c r="B11" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>135724188</v>
       </c>
       <c r="B12" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>135724192</v>
       </c>
       <c r="B13" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>135724194</v>
       </c>
       <c r="B14" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>135724211</v>
       </c>
       <c r="B15" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135724212</v>
       </c>
       <c r="B16" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135724220</v>
       </c>
       <c r="B17" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135724227</v>
       </c>
       <c r="B18" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135724230</v>
       </c>
       <c r="B19" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>135724234</v>
       </c>
       <c r="B20" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>135724206</v>
       </c>
       <c r="B21" t="n">
-        <v>91582</v>
+        <v>91584</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>135724181</v>
       </c>
       <c r="B22" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>135724216</v>
       </c>
       <c r="B23" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>135724208</v>
       </c>
       <c r="B24" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>135724221</v>
       </c>
       <c r="B25" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>135724224</v>
       </c>
       <c r="B26" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>135724225</v>
       </c>
       <c r="B27" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>135724228</v>
       </c>
       <c r="B28" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>135724235</v>
       </c>
       <c r="B29" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>135724222</v>
       </c>
       <c r="B30" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>135724226</v>
       </c>
       <c r="B31" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>135724209</v>
       </c>
       <c r="B32" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>135724185</v>
       </c>
       <c r="B33" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>135724244</v>
       </c>
       <c r="B34" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135724180</v>
       </c>
       <c r="B35" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>135724233</v>
       </c>
       <c r="B36" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>135724240</v>
       </c>
       <c r="B37" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>135724215</v>
       </c>
       <c r="B38" t="n">
-        <v>99175</v>
+        <v>99192</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>135724196</v>
       </c>
       <c r="B39" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>135724202</v>
       </c>
       <c r="B40" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>135724203</v>
       </c>
       <c r="B41" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>135724204</v>
       </c>
       <c r="B42" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135724205</v>
       </c>
       <c r="B43" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>135724207</v>
       </c>
       <c r="B44" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>135724213</v>
       </c>
       <c r="B45" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>135724218</v>
       </c>
       <c r="B46" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>135724223</v>
       </c>
       <c r="B47" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135724236</v>
       </c>
       <c r="B48" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>135724237</v>
       </c>
       <c r="B49" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>135724238</v>
       </c>
       <c r="B50" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>135724241</v>
       </c>
       <c r="B51" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>135724187</v>
       </c>
       <c r="B52" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>135724191</v>
       </c>
       <c r="B53" t="n">
-        <v>99553</v>
+        <v>99570</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>135724199</v>
       </c>
       <c r="B54" t="n">
-        <v>99553</v>
+        <v>99570</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>135724186</v>
       </c>
       <c r="B55" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135724200</v>
       </c>
       <c r="B56" t="n">
-        <v>92442</v>
+        <v>92456</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135724195</v>
       </c>
       <c r="B57" t="n">
-        <v>93370</v>
+        <v>93385</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 31349-2026 artfynd.xlsx
+++ b/artfynd/A 31349-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724189</v>
       </c>
       <c r="B2" t="n">
-        <v>92014</v>
+        <v>92015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135724197</v>
       </c>
       <c r="B3" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135724214</v>
       </c>
       <c r="B4" t="n">
-        <v>92450</v>
+        <v>92451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>135724184</v>
       </c>
       <c r="B5" t="n">
-        <v>91596</v>
+        <v>91597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>135724190</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>135724198</v>
       </c>
       <c r="B7" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135724243</v>
       </c>
       <c r="B8" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>135724242</v>
       </c>
       <c r="B9" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>135724182</v>
       </c>
       <c r="B10" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135724183</v>
       </c>
       <c r="B11" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>135724188</v>
       </c>
       <c r="B12" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>135724192</v>
       </c>
       <c r="B13" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>135724194</v>
       </c>
       <c r="B14" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>135724211</v>
       </c>
       <c r="B15" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135724212</v>
       </c>
       <c r="B16" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135724220</v>
       </c>
       <c r="B17" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135724227</v>
       </c>
       <c r="B18" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135724230</v>
       </c>
       <c r="B19" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>135724234</v>
       </c>
       <c r="B20" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>135724206</v>
       </c>
       <c r="B21" t="n">
-        <v>91584</v>
+        <v>91585</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>135724181</v>
       </c>
       <c r="B22" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>135724216</v>
       </c>
       <c r="B23" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>135724208</v>
       </c>
       <c r="B24" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>135724221</v>
       </c>
       <c r="B25" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>135724224</v>
       </c>
       <c r="B26" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>135724225</v>
       </c>
       <c r="B27" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>135724228</v>
       </c>
       <c r="B28" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>135724235</v>
       </c>
       <c r="B29" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>135724222</v>
       </c>
       <c r="B30" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>135724226</v>
       </c>
       <c r="B31" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>135724209</v>
       </c>
       <c r="B32" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>135724215</v>
       </c>
       <c r="B38" t="n">
-        <v>99192</v>
+        <v>99193</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>135724196</v>
       </c>
       <c r="B39" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>135724202</v>
       </c>
       <c r="B40" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>135724203</v>
       </c>
       <c r="B41" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>135724204</v>
       </c>
       <c r="B42" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135724205</v>
       </c>
       <c r="B43" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>135724207</v>
       </c>
       <c r="B44" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>135724213</v>
       </c>
       <c r="B45" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>135724218</v>
       </c>
       <c r="B46" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>135724223</v>
       </c>
       <c r="B47" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135724236</v>
       </c>
       <c r="B48" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>135724237</v>
       </c>
       <c r="B49" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>135724238</v>
       </c>
       <c r="B50" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>135724241</v>
       </c>
       <c r="B51" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>135724187</v>
       </c>
       <c r="B52" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>135724191</v>
       </c>
       <c r="B53" t="n">
-        <v>99570</v>
+        <v>99571</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>135724199</v>
       </c>
       <c r="B54" t="n">
-        <v>99570</v>
+        <v>99571</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>135724186</v>
       </c>
       <c r="B55" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135724200</v>
       </c>
       <c r="B56" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135724195</v>
       </c>
       <c r="B57" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 31349-2026 artfynd.xlsx
+++ b/artfynd/A 31349-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724189</v>
       </c>
       <c r="B2" t="n">
-        <v>92015</v>
+        <v>92016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135724197</v>
       </c>
       <c r="B3" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135724214</v>
       </c>
       <c r="B4" t="n">
-        <v>92451</v>
+        <v>92452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>135724184</v>
       </c>
       <c r="B5" t="n">
-        <v>91597</v>
+        <v>91598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>135724190</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>135724198</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135724243</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>135724242</v>
       </c>
       <c r="B9" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>135724182</v>
       </c>
       <c r="B10" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135724183</v>
       </c>
       <c r="B11" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>135724188</v>
       </c>
       <c r="B12" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>135724192</v>
       </c>
       <c r="B13" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>135724194</v>
       </c>
       <c r="B14" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>135724211</v>
       </c>
       <c r="B15" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135724212</v>
       </c>
       <c r="B16" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135724220</v>
       </c>
       <c r="B17" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135724227</v>
       </c>
       <c r="B18" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135724230</v>
       </c>
       <c r="B19" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>135724234</v>
       </c>
       <c r="B20" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>135724206</v>
       </c>
       <c r="B21" t="n">
-        <v>91585</v>
+        <v>91586</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>135724215</v>
       </c>
       <c r="B38" t="n">
-        <v>99193</v>
+        <v>99194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>135724196</v>
       </c>
       <c r="B39" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>135724202</v>
       </c>
       <c r="B40" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>135724203</v>
       </c>
       <c r="B41" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>135724204</v>
       </c>
       <c r="B42" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135724205</v>
       </c>
       <c r="B43" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>135724207</v>
       </c>
       <c r="B44" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>135724213</v>
       </c>
       <c r="B45" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>135724218</v>
       </c>
       <c r="B46" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>135724223</v>
       </c>
       <c r="B47" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135724236</v>
       </c>
       <c r="B48" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>135724237</v>
       </c>
       <c r="B49" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>135724238</v>
       </c>
       <c r="B50" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>135724241</v>
       </c>
       <c r="B51" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>135724187</v>
       </c>
       <c r="B52" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>135724191</v>
       </c>
       <c r="B53" t="n">
-        <v>99571</v>
+        <v>99572</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>135724199</v>
       </c>
       <c r="B54" t="n">
-        <v>99571</v>
+        <v>99572</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>135724186</v>
       </c>
       <c r="B55" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135724200</v>
       </c>
       <c r="B56" t="n">
-        <v>92457</v>
+        <v>92458</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135724195</v>
       </c>
       <c r="B57" t="n">
-        <v>93386</v>
+        <v>93387</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 31349-2026 artfynd.xlsx
+++ b/artfynd/A 31349-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724189</v>
       </c>
       <c r="B2" t="n">
-        <v>92016</v>
+        <v>92017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135724197</v>
       </c>
       <c r="B3" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135724214</v>
       </c>
       <c r="B4" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>135724184</v>
       </c>
       <c r="B5" t="n">
-        <v>91598</v>
+        <v>91599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>135724190</v>
       </c>
       <c r="B6" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>135724198</v>
       </c>
       <c r="B7" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135724243</v>
       </c>
       <c r="B8" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>135724242</v>
       </c>
       <c r="B9" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>135724182</v>
       </c>
       <c r="B10" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135724183</v>
       </c>
       <c r="B11" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>135724188</v>
       </c>
       <c r="B12" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>135724192</v>
       </c>
       <c r="B13" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>135724194</v>
       </c>
       <c r="B14" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>135724211</v>
       </c>
       <c r="B15" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135724212</v>
       </c>
       <c r="B16" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135724220</v>
       </c>
       <c r="B17" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135724227</v>
       </c>
       <c r="B18" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135724230</v>
       </c>
       <c r="B19" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>135724234</v>
       </c>
       <c r="B20" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>135724206</v>
       </c>
       <c r="B21" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>135724181</v>
       </c>
       <c r="B22" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>135724216</v>
       </c>
       <c r="B23" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>135724208</v>
       </c>
       <c r="B24" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>135724221</v>
       </c>
       <c r="B25" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>135724224</v>
       </c>
       <c r="B26" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>135724225</v>
       </c>
       <c r="B27" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>135724228</v>
       </c>
       <c r="B28" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>135724235</v>
       </c>
       <c r="B29" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>135724222</v>
       </c>
       <c r="B30" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>135724226</v>
       </c>
       <c r="B31" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>135724209</v>
       </c>
       <c r="B32" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>135724185</v>
       </c>
       <c r="B33" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>135724244</v>
       </c>
       <c r="B34" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135724180</v>
       </c>
       <c r="B35" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>135724233</v>
       </c>
       <c r="B36" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>135724240</v>
       </c>
       <c r="B37" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>135724215</v>
       </c>
       <c r="B38" t="n">
-        <v>99194</v>
+        <v>99195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>135724196</v>
       </c>
       <c r="B39" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>135724202</v>
       </c>
       <c r="B40" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>135724203</v>
       </c>
       <c r="B41" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>135724204</v>
       </c>
       <c r="B42" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135724205</v>
       </c>
       <c r="B43" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>135724207</v>
       </c>
       <c r="B44" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>135724213</v>
       </c>
       <c r="B45" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>135724218</v>
       </c>
       <c r="B46" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>135724223</v>
       </c>
       <c r="B47" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135724236</v>
       </c>
       <c r="B48" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>135724237</v>
       </c>
       <c r="B49" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>135724238</v>
       </c>
       <c r="B50" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>135724241</v>
       </c>
       <c r="B51" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>135724187</v>
       </c>
       <c r="B52" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>135724191</v>
       </c>
       <c r="B53" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>135724199</v>
       </c>
       <c r="B54" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>135724186</v>
       </c>
       <c r="B55" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135724200</v>
       </c>
       <c r="B56" t="n">
-        <v>92458</v>
+        <v>92459</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135724195</v>
       </c>
       <c r="B57" t="n">
-        <v>93387</v>
+        <v>93388</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 31349-2026 artfynd.xlsx
+++ b/artfynd/A 31349-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724189</v>
       </c>
       <c r="B2" t="n">
-        <v>92017</v>
+        <v>92023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135724197</v>
       </c>
       <c r="B3" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135724214</v>
       </c>
       <c r="B4" t="n">
-        <v>92453</v>
+        <v>92459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>135724184</v>
       </c>
       <c r="B5" t="n">
-        <v>91599</v>
+        <v>91605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>135724190</v>
       </c>
       <c r="B6" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>135724198</v>
       </c>
       <c r="B7" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135724243</v>
       </c>
       <c r="B8" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>135724242</v>
       </c>
       <c r="B9" t="n">
-        <v>92409</v>
+        <v>92415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>135724182</v>
       </c>
       <c r="B10" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135724183</v>
       </c>
       <c r="B11" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>135724188</v>
       </c>
       <c r="B12" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>135724192</v>
       </c>
       <c r="B13" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>135724194</v>
       </c>
       <c r="B14" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>135724211</v>
       </c>
       <c r="B15" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135724212</v>
       </c>
       <c r="B16" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135724220</v>
       </c>
       <c r="B17" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135724227</v>
       </c>
       <c r="B18" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135724230</v>
       </c>
       <c r="B19" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>135724234</v>
       </c>
       <c r="B20" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>135724206</v>
       </c>
       <c r="B21" t="n">
-        <v>91587</v>
+        <v>91593</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>135724181</v>
       </c>
       <c r="B22" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>135724216</v>
       </c>
       <c r="B23" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>135724208</v>
       </c>
       <c r="B24" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>135724221</v>
       </c>
       <c r="B25" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>135724224</v>
       </c>
       <c r="B26" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>135724225</v>
       </c>
       <c r="B27" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>135724228</v>
       </c>
       <c r="B28" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>135724235</v>
       </c>
       <c r="B29" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>135724222</v>
       </c>
       <c r="B30" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>135724226</v>
       </c>
       <c r="B31" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>135724209</v>
       </c>
       <c r="B32" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>135724185</v>
       </c>
       <c r="B33" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>135724244</v>
       </c>
       <c r="B34" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135724180</v>
       </c>
       <c r="B35" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>135724233</v>
       </c>
       <c r="B36" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>135724240</v>
       </c>
       <c r="B37" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>135724215</v>
       </c>
       <c r="B38" t="n">
-        <v>99195</v>
+        <v>99201</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>135724196</v>
       </c>
       <c r="B39" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>135724202</v>
       </c>
       <c r="B40" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>135724203</v>
       </c>
       <c r="B41" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>135724204</v>
       </c>
       <c r="B42" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135724205</v>
       </c>
       <c r="B43" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>135724207</v>
       </c>
       <c r="B44" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>135724213</v>
       </c>
       <c r="B45" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>135724218</v>
       </c>
       <c r="B46" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>135724223</v>
       </c>
       <c r="B47" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135724236</v>
       </c>
       <c r="B48" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>135724237</v>
       </c>
       <c r="B49" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>135724238</v>
       </c>
       <c r="B50" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>135724241</v>
       </c>
       <c r="B51" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>135724187</v>
       </c>
       <c r="B52" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>135724191</v>
       </c>
       <c r="B53" t="n">
-        <v>99573</v>
+        <v>99579</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>135724199</v>
       </c>
       <c r="B54" t="n">
-        <v>99573</v>
+        <v>99579</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>135724186</v>
       </c>
       <c r="B55" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135724200</v>
       </c>
       <c r="B56" t="n">
-        <v>92459</v>
+        <v>92465</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135724195</v>
       </c>
       <c r="B57" t="n">
-        <v>93388</v>
+        <v>93394</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 31349-2026 artfynd.xlsx
+++ b/artfynd/A 31349-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724189</v>
       </c>
       <c r="B2" t="n">
-        <v>92023</v>
+        <v>92024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135724197</v>
       </c>
       <c r="B3" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135724214</v>
       </c>
       <c r="B4" t="n">
-        <v>92459</v>
+        <v>92460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>135724184</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>135724190</v>
       </c>
       <c r="B6" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>135724198</v>
       </c>
       <c r="B7" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135724243</v>
       </c>
       <c r="B8" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>135724242</v>
       </c>
       <c r="B9" t="n">
-        <v>92415</v>
+        <v>92416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>135724182</v>
       </c>
       <c r="B10" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135724183</v>
       </c>
       <c r="B11" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>135724188</v>
       </c>
       <c r="B12" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>135724192</v>
       </c>
       <c r="B13" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>135724194</v>
       </c>
       <c r="B14" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>135724211</v>
       </c>
       <c r="B15" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135724212</v>
       </c>
       <c r="B16" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135724220</v>
       </c>
       <c r="B17" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135724227</v>
       </c>
       <c r="B18" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135724230</v>
       </c>
       <c r="B19" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>135724234</v>
       </c>
       <c r="B20" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>135724206</v>
       </c>
       <c r="B21" t="n">
-        <v>91593</v>
+        <v>91594</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>135724181</v>
       </c>
       <c r="B22" t="n">
-        <v>80458</v>
+        <v>80459</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>135724216</v>
       </c>
       <c r="B23" t="n">
-        <v>80458</v>
+        <v>80459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>135724208</v>
       </c>
       <c r="B24" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>135724221</v>
       </c>
       <c r="B25" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>135724224</v>
       </c>
       <c r="B26" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>135724225</v>
       </c>
       <c r="B27" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>135724228</v>
       </c>
       <c r="B28" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>135724235</v>
       </c>
       <c r="B29" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>135724222</v>
       </c>
       <c r="B30" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>135724226</v>
       </c>
       <c r="B31" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>135724209</v>
       </c>
       <c r="B32" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>135724185</v>
       </c>
       <c r="B33" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>135724244</v>
       </c>
       <c r="B34" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135724180</v>
       </c>
       <c r="B35" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>135724233</v>
       </c>
       <c r="B36" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>135724240</v>
       </c>
       <c r="B37" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>135724215</v>
       </c>
       <c r="B38" t="n">
-        <v>99201</v>
+        <v>99202</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>135724196</v>
       </c>
       <c r="B39" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>135724202</v>
       </c>
       <c r="B40" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>135724203</v>
       </c>
       <c r="B41" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>135724204</v>
       </c>
       <c r="B42" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135724205</v>
       </c>
       <c r="B43" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>135724207</v>
       </c>
       <c r="B44" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>135724213</v>
       </c>
       <c r="B45" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>135724218</v>
       </c>
       <c r="B46" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>135724223</v>
       </c>
       <c r="B47" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135724236</v>
       </c>
       <c r="B48" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>135724237</v>
       </c>
       <c r="B49" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>135724238</v>
       </c>
       <c r="B50" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>135724241</v>
       </c>
       <c r="B51" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>135724187</v>
       </c>
       <c r="B52" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>135724191</v>
       </c>
       <c r="B53" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>135724199</v>
       </c>
       <c r="B54" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>135724186</v>
       </c>
       <c r="B55" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135724200</v>
       </c>
       <c r="B56" t="n">
-        <v>92465</v>
+        <v>92466</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135724195</v>
       </c>
       <c r="B57" t="n">
-        <v>93394</v>
+        <v>93395</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7180,6 +7180,11 @@
       </c>
       <c r="E57" t="n">
         <v>6331649</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Huldretaggsvamp</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>

--- a/artfynd/A 31349-2026 artfynd.xlsx
+++ b/artfynd/A 31349-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724189</v>
       </c>
       <c r="B2" t="n">
-        <v>92024</v>
+        <v>92030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135724197</v>
       </c>
       <c r="B3" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135724214</v>
       </c>
       <c r="B4" t="n">
-        <v>92460</v>
+        <v>92466</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>135724184</v>
       </c>
       <c r="B5" t="n">
-        <v>91606</v>
+        <v>91612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>135724190</v>
       </c>
       <c r="B6" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>135724198</v>
       </c>
       <c r="B7" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135724243</v>
       </c>
       <c r="B8" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>135724242</v>
       </c>
       <c r="B9" t="n">
-        <v>92416</v>
+        <v>92422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>135724182</v>
       </c>
       <c r="B10" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135724183</v>
       </c>
       <c r="B11" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>135724188</v>
       </c>
       <c r="B12" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>135724192</v>
       </c>
       <c r="B13" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>135724194</v>
       </c>
       <c r="B14" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>135724211</v>
       </c>
       <c r="B15" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135724212</v>
       </c>
       <c r="B16" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135724220</v>
       </c>
       <c r="B17" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135724227</v>
       </c>
       <c r="B18" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135724230</v>
       </c>
       <c r="B19" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>135724234</v>
       </c>
       <c r="B20" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>135724206</v>
       </c>
       <c r="B21" t="n">
-        <v>91594</v>
+        <v>91600</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>135724181</v>
       </c>
       <c r="B22" t="n">
-        <v>80459</v>
+        <v>80463</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>135724216</v>
       </c>
       <c r="B23" t="n">
-        <v>80459</v>
+        <v>80463</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>135724208</v>
       </c>
       <c r="B24" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>135724221</v>
       </c>
       <c r="B25" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>135724224</v>
       </c>
       <c r="B26" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>135724225</v>
       </c>
       <c r="B27" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>135724228</v>
       </c>
       <c r="B28" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>135724235</v>
       </c>
       <c r="B29" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>135724222</v>
       </c>
       <c r="B30" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>135724226</v>
       </c>
       <c r="B31" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>135724209</v>
       </c>
       <c r="B32" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>135724215</v>
       </c>
       <c r="B38" t="n">
-        <v>99202</v>
+        <v>99213</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>135724196</v>
       </c>
       <c r="B39" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>135724202</v>
       </c>
       <c r="B40" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>135724203</v>
       </c>
       <c r="B41" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>135724204</v>
       </c>
       <c r="B42" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135724205</v>
       </c>
       <c r="B43" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>135724207</v>
       </c>
       <c r="B44" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>135724213</v>
       </c>
       <c r="B45" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>135724218</v>
       </c>
       <c r="B46" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>135724223</v>
       </c>
       <c r="B47" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135724236</v>
       </c>
       <c r="B48" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>135724237</v>
       </c>
       <c r="B49" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>135724238</v>
       </c>
       <c r="B50" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>135724241</v>
       </c>
       <c r="B51" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>135724187</v>
       </c>
       <c r="B52" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>135724191</v>
       </c>
       <c r="B53" t="n">
-        <v>99580</v>
+        <v>99591</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>135724199</v>
       </c>
       <c r="B54" t="n">
-        <v>99580</v>
+        <v>99591</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>135724186</v>
       </c>
       <c r="B55" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135724200</v>
       </c>
       <c r="B56" t="n">
-        <v>92466</v>
+        <v>92472</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135724195</v>
       </c>
       <c r="B57" t="n">
-        <v>93395</v>
+        <v>93401</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 31349-2026 artfynd.xlsx
+++ b/artfynd/A 31349-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724189</v>
       </c>
       <c r="B2" t="n">
-        <v>92030</v>
+        <v>92037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135724197</v>
       </c>
       <c r="B3" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135724214</v>
       </c>
       <c r="B4" t="n">
-        <v>92466</v>
+        <v>92473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>135724184</v>
       </c>
       <c r="B5" t="n">
-        <v>91612</v>
+        <v>91619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>135724190</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>135724198</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135724243</v>
       </c>
       <c r="B8" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>135724242</v>
       </c>
       <c r="B9" t="n">
-        <v>92422</v>
+        <v>92429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>135724182</v>
       </c>
       <c r="B10" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135724183</v>
       </c>
       <c r="B11" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>135724188</v>
       </c>
       <c r="B12" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>135724192</v>
       </c>
       <c r="B13" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>135724194</v>
       </c>
       <c r="B14" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>135724211</v>
       </c>
       <c r="B15" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135724212</v>
       </c>
       <c r="B16" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135724220</v>
       </c>
       <c r="B17" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135724227</v>
       </c>
       <c r="B18" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135724230</v>
       </c>
       <c r="B19" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>135724234</v>
       </c>
       <c r="B20" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>135724206</v>
       </c>
       <c r="B21" t="n">
-        <v>91600</v>
+        <v>91607</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>135724181</v>
       </c>
       <c r="B22" t="n">
-        <v>80463</v>
+        <v>80469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>135724216</v>
       </c>
       <c r="B23" t="n">
-        <v>80463</v>
+        <v>80469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>135724208</v>
       </c>
       <c r="B24" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>135724221</v>
       </c>
       <c r="B25" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>135724224</v>
       </c>
       <c r="B26" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>135724225</v>
       </c>
       <c r="B27" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>135724228</v>
       </c>
       <c r="B28" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>135724235</v>
       </c>
       <c r="B29" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>135724222</v>
       </c>
       <c r="B30" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>135724226</v>
       </c>
       <c r="B31" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>135724209</v>
       </c>
       <c r="B32" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>135724185</v>
       </c>
       <c r="B33" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>135724244</v>
       </c>
       <c r="B34" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>135724180</v>
       </c>
       <c r="B35" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>135724233</v>
       </c>
       <c r="B36" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>135724240</v>
       </c>
       <c r="B37" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>135724215</v>
       </c>
       <c r="B38" t="n">
-        <v>99213</v>
+        <v>99226</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>135724196</v>
       </c>
       <c r="B39" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>135724202</v>
       </c>
       <c r="B40" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>135724203</v>
       </c>
       <c r="B41" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>135724204</v>
       </c>
       <c r="B42" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135724205</v>
       </c>
       <c r="B43" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>135724207</v>
       </c>
       <c r="B44" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>135724213</v>
       </c>
       <c r="B45" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>135724218</v>
       </c>
       <c r="B46" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>135724223</v>
       </c>
       <c r="B47" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135724236</v>
       </c>
       <c r="B48" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>135724237</v>
       </c>
       <c r="B49" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>135724238</v>
       </c>
       <c r="B50" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>135724241</v>
       </c>
       <c r="B51" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>135724187</v>
       </c>
       <c r="B52" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>135724191</v>
       </c>
       <c r="B53" t="n">
-        <v>99591</v>
+        <v>99604</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>135724199</v>
       </c>
       <c r="B54" t="n">
-        <v>99591</v>
+        <v>99604</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>135724186</v>
       </c>
       <c r="B55" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135724200</v>
       </c>
       <c r="B56" t="n">
-        <v>92472</v>
+        <v>92479</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135724195</v>
       </c>
       <c r="B57" t="n">
-        <v>93401</v>
+        <v>93408</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 31349-2026 artfynd.xlsx
+++ b/artfynd/A 31349-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724189</v>
       </c>
       <c r="B2" t="n">
-        <v>92037</v>
+        <v>92038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135724197</v>
       </c>
       <c r="B3" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135724214</v>
       </c>
       <c r="B4" t="n">
-        <v>92473</v>
+        <v>92474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>135724184</v>
       </c>
       <c r="B5" t="n">
-        <v>91619</v>
+        <v>91620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>135724190</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>135724198</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>135724243</v>
       </c>
       <c r="B8" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>135724242</v>
       </c>
       <c r="B9" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>135724182</v>
       </c>
       <c r="B10" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>135724183</v>
       </c>
       <c r="B11" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>135724188</v>
       </c>
       <c r="B12" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>135724192</v>
       </c>
       <c r="B13" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>135724194</v>
       </c>
       <c r="B14" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>135724211</v>
       </c>
       <c r="B15" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135724212</v>
       </c>
       <c r="B16" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>135724220</v>
       </c>
       <c r="B17" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135724227</v>
       </c>
       <c r="B18" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135724230</v>
       </c>
       <c r="B19" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>135724234</v>
       </c>
       <c r="B20" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>135724206</v>
       </c>
       <c r="B21" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>135724215</v>
       </c>
       <c r="B38" t="n">
-        <v>99226</v>
+        <v>99227</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>135724196</v>
       </c>
       <c r="B39" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5188,7 +5188,7 @@
         <v>135724202</v>
       </c>
       <c r="B40" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         <v>135724203</v>
       </c>
       <c r="B41" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>135724204</v>
       </c>
       <c r="B42" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>135724205</v>
       </c>
       <c r="B43" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>135724207</v>
       </c>
       <c r="B44" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>135724213</v>
       </c>
       <c r="B45" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>135724218</v>
       </c>
       <c r="B46" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>135724223</v>
       </c>
       <c r="B47" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135724236</v>
       </c>
       <c r="B48" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>135724237</v>
       </c>
       <c r="B49" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>135724238</v>
       </c>
       <c r="B50" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>135724241</v>
       </c>
       <c r="B51" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         <v>135724187</v>
       </c>
       <c r="B52" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>135724191</v>
       </c>
       <c r="B53" t="n">
-        <v>99604</v>
+        <v>99605</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>135724199</v>
       </c>
       <c r="B54" t="n">
-        <v>99604</v>
+        <v>99605</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>135724186</v>
       </c>
       <c r="B55" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135724200</v>
       </c>
       <c r="B56" t="n">
-        <v>92479</v>
+        <v>92480</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>135724195</v>
       </c>
       <c r="B57" t="n">
-        <v>93408</v>
+        <v>93409</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 31349-2026 artfynd.xlsx
+++ b/artfynd/A 31349-2026 artfynd.xlsx
@@ -2921,7 +2921,7 @@
         <v>135724206</v>
       </c>
       <c r="B21" t="n">
-        <v>91608</v>
+        <v>91621</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 31349-2026 artfynd.xlsx
+++ b/artfynd/A 31349-2026 artfynd.xlsx
@@ -2921,7 +2921,7 @@
         <v>135724206</v>
       </c>
       <c r="B21" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
